--- a/Services/Fsel.Interaction/Fsel.Interaction.Api/Resources/ExportExcelTemplates/SurveyQuestionReportSchool.xlsx
+++ b/Services/Fsel.Interaction/Fsel.Interaction.Api/Resources/ExportExcelTemplates/SurveyQuestionReportSchool.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Backend\fsel_src\Services\Fsel.Interaction\Fsel.Interaction.Api\Resources\ExportExcelTemplates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF7BC17F-AE23-4519-9950-DA2F948D991B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{117D33F5-CA59-47A5-BD5D-72CA215DE281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-135" windowWidth="29040" windowHeight="15720" xr2:uid="{100E73E1-3CC8-4AF7-99B2-BDB29FF385FB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{100E73E1-3CC8-4AF7-99B2-BDB29FF385FB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
   <si>
     <t>STT</t>
   </si>
@@ -45,12 +45,6 @@
     <t>đăng ký tham gia</t>
   </si>
   <si>
-    <t>đăng ký tài khoản thực tế</t>
-  </si>
-  <si>
-    <t>tham gia thực tế</t>
-  </si>
-  <si>
     <t>Đã hoàn thành PT</t>
   </si>
   <si>
@@ -61,6 +55,9 @@
   </si>
   <si>
     <t>Trả lời Câu hỏi Khảo sát {0}</t>
+  </si>
+  <si>
+    <t>đã xác thực</t>
   </si>
 </sst>
 </file>
@@ -112,7 +109,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -135,15 +132,38 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -152,6 +172,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -471,22 +500,22 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
+      <c r="A1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -509,36 +538,36 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="2" t="s">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="G3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -546,11 +575,11 @@
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="H3:H4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
